--- a/output/yearly_total_coral_cover_iteration_100_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_100_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.259019208638318</v>
+        <v>1.251793545535062</v>
       </c>
       <c r="C3" t="n">
-        <v>4.650074399413194</v>
+        <v>4.602066936675524</v>
       </c>
       <c r="D3" t="n">
-        <v>6.124549698323506</v>
+        <v>6.168453455657422</v>
       </c>
       <c r="E3" t="n">
-        <v>12.03364330637502</v>
+        <v>12.02231393786801</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.385424455555559</v>
+        <v>1.365673632633429</v>
       </c>
       <c r="C4" t="n">
-        <v>5.209396264193263</v>
+        <v>5.090192801582525</v>
       </c>
       <c r="D4" t="n">
-        <v>6.472087629006208</v>
+        <v>6.51893685779255</v>
       </c>
       <c r="E4" t="n">
-        <v>13.06690834875503</v>
+        <v>12.9748032920085</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.559124002736228</v>
+        <v>1.519373047167374</v>
       </c>
       <c r="C5" t="n">
-        <v>5.909572994611598</v>
+        <v>5.703515569172376</v>
       </c>
       <c r="D5" t="n">
-        <v>6.809059636513778</v>
+        <v>6.95851522509552</v>
       </c>
       <c r="E5" t="n">
-        <v>14.27775663386161</v>
+        <v>14.18140384143527</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.756941029131235</v>
+        <v>1.689849096978216</v>
       </c>
       <c r="C6" t="n">
-        <v>6.813561903432505</v>
+        <v>6.4794813929949</v>
       </c>
       <c r="D6" t="n">
-        <v>7.221752173057887</v>
+        <v>7.492665628533595</v>
       </c>
       <c r="E6" t="n">
-        <v>15.79225510562163</v>
+        <v>15.66199611850671</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.976056038611775</v>
+        <v>1.88420386188766</v>
       </c>
       <c r="C7" t="n">
-        <v>7.847337022021089</v>
+        <v>7.430199870922486</v>
       </c>
       <c r="D7" t="n">
-        <v>7.614531455409952</v>
+        <v>8.017630563950735</v>
       </c>
       <c r="E7" t="n">
-        <v>17.43792451604282</v>
+        <v>17.33203429676088</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.192243045789334</v>
+        <v>1.118685788078275</v>
       </c>
       <c r="C8" t="n">
-        <v>5.512034704579492</v>
+        <v>5.148552365935014</v>
       </c>
       <c r="D8" t="n">
-        <v>5.942455527561651</v>
+        <v>6.293667910199371</v>
       </c>
       <c r="E8" t="n">
-        <v>12.64673327793048</v>
+        <v>12.56090606421266</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.483705881463597</v>
+        <v>1.389972316740242</v>
       </c>
       <c r="C9" t="n">
-        <v>6.799135851176336</v>
+        <v>6.35605756668662</v>
       </c>
       <c r="D9" t="n">
-        <v>6.489821404734521</v>
+        <v>6.938590877381378</v>
       </c>
       <c r="E9" t="n">
-        <v>14.77266313737445</v>
+        <v>14.68462076080824</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.783376307741785</v>
+        <v>1.669299387774301</v>
       </c>
       <c r="C10" t="n">
-        <v>8.261742829779179</v>
+        <v>7.693838391461152</v>
       </c>
       <c r="D10" t="n">
-        <v>7.029979351020195</v>
+        <v>7.537214694307989</v>
       </c>
       <c r="E10" t="n">
-        <v>17.07509848854116</v>
+        <v>16.90035247354344</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.078380326898252</v>
+        <v>1.953499419535788</v>
       </c>
       <c r="C11" t="n">
-        <v>9.820355925034512</v>
+        <v>9.12067086143132</v>
       </c>
       <c r="D11" t="n">
-        <v>7.520924527362423</v>
+        <v>8.118079786565318</v>
       </c>
       <c r="E11" t="n">
-        <v>19.41966077929519</v>
+        <v>19.19225006753242</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.359762839690265</v>
+        <v>2.247388132394568</v>
       </c>
       <c r="C12" t="n">
-        <v>11.45978303363657</v>
+        <v>10.5901293797158</v>
       </c>
       <c r="D12" t="n">
-        <v>7.97783551504779</v>
+        <v>8.785152983664643</v>
       </c>
       <c r="E12" t="n">
-        <v>21.79738138837462</v>
+        <v>21.62267049577501</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.632932454553817</v>
+        <v>2.529917868447129</v>
       </c>
       <c r="C13" t="n">
-        <v>13.11314044220885</v>
+        <v>12.04449113793115</v>
       </c>
       <c r="D13" t="n">
-        <v>8.56807175036518</v>
+        <v>9.44937218887689</v>
       </c>
       <c r="E13" t="n">
-        <v>24.31414464712785</v>
+        <v>24.02378119525517</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.519038587827005</v>
+        <v>1.459760661444582</v>
       </c>
       <c r="C14" t="n">
-        <v>9.147552044044167</v>
+        <v>8.371166324571703</v>
       </c>
       <c r="D14" t="n">
-        <v>6.473124035520217</v>
+        <v>7.115638638041585</v>
       </c>
       <c r="E14" t="n">
-        <v>17.13971466739139</v>
+        <v>16.94656562405787</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.531251529267835</v>
+        <v>1.495133031228595</v>
       </c>
       <c r="C15" t="n">
-        <v>9.858896978110275</v>
+        <v>8.916821698592079</v>
       </c>
       <c r="D15" t="n">
-        <v>6.506640902143203</v>
+        <v>7.234911166630529</v>
       </c>
       <c r="E15" t="n">
-        <v>17.89678940952131</v>
+        <v>17.6468658964512</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.762148771829643</v>
+        <v>1.73608337028189</v>
       </c>
       <c r="C16" t="n">
-        <v>11.64495130653833</v>
+        <v>10.40552428235786</v>
       </c>
       <c r="D16" t="n">
-        <v>6.978321586648583</v>
+        <v>7.825020076699203</v>
       </c>
       <c r="E16" t="n">
-        <v>20.38542166501655</v>
+        <v>19.96662772933895</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.405116584226205</v>
+        <v>1.398234532819435</v>
       </c>
       <c r="C17" t="n">
-        <v>10.71743534547411</v>
+        <v>9.479854006977627</v>
       </c>
       <c r="D17" t="n">
-        <v>6.486446351866846</v>
+        <v>7.341587872173988</v>
       </c>
       <c r="E17" t="n">
-        <v>18.60899828156716</v>
+        <v>18.21967641197105</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.588605230149934</v>
+        <v>1.594132469724843</v>
       </c>
       <c r="C18" t="n">
-        <v>12.52574589435744</v>
+        <v>10.9611345780993</v>
       </c>
       <c r="D18" t="n">
-        <v>6.901637273469865</v>
+        <v>7.871348750862609</v>
       </c>
       <c r="E18" t="n">
-        <v>21.01598839797724</v>
+        <v>20.42661579868675</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.579700778472416</v>
+        <v>1.599698979207923</v>
       </c>
       <c r="C19" t="n">
-        <v>13.44595765250206</v>
+        <v>11.64932990129927</v>
       </c>
       <c r="D19" t="n">
-        <v>6.980883948156668</v>
+        <v>8.054857031740422</v>
       </c>
       <c r="E19" t="n">
-        <v>22.00654237913114</v>
+        <v>21.30388591224762</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.742288015772729</v>
+        <v>1.773919926803562</v>
       </c>
       <c r="C20" t="n">
-        <v>15.47195111984803</v>
+        <v>13.33125025073786</v>
       </c>
       <c r="D20" t="n">
-        <v>7.41092871252494</v>
+        <v>8.598912157002879</v>
       </c>
       <c r="E20" t="n">
-        <v>24.6251678481457</v>
+        <v>23.7040823345443</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.030295128221815</v>
+        <v>1.050705662993106</v>
       </c>
       <c r="C21" t="n">
-        <v>11.39547939741217</v>
+        <v>9.780651686081807</v>
       </c>
       <c r="D21" t="n">
-        <v>6.177284182322484</v>
+        <v>7.220901626890927</v>
       </c>
       <c r="E21" t="n">
-        <v>18.60305870795647</v>
+        <v>18.05225897596584</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_100_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_100_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.251793545535062</v>
+        <v>1.29088673911817</v>
       </c>
       <c r="C3" t="n">
-        <v>4.602066936675524</v>
+        <v>4.593938065684362</v>
       </c>
       <c r="D3" t="n">
-        <v>6.168453455657422</v>
+        <v>6.114349339676381</v>
       </c>
       <c r="E3" t="n">
-        <v>12.02231393786801</v>
+        <v>11.99917414447891</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.365673632633429</v>
+        <v>1.471097668225085</v>
       </c>
       <c r="C4" t="n">
-        <v>5.090192801582525</v>
+        <v>5.017043914170736</v>
       </c>
       <c r="D4" t="n">
-        <v>6.51893685779255</v>
+        <v>6.403424889629651</v>
       </c>
       <c r="E4" t="n">
-        <v>12.9748032920085</v>
+        <v>12.89156647202547</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.519373047167374</v>
+        <v>1.710078247576866</v>
       </c>
       <c r="C5" t="n">
-        <v>5.703515569172376</v>
+        <v>5.524204855809763</v>
       </c>
       <c r="D5" t="n">
-        <v>6.95851522509552</v>
+        <v>6.712130286668832</v>
       </c>
       <c r="E5" t="n">
-        <v>14.18140384143527</v>
+        <v>13.94641339005546</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.689849096978216</v>
+        <v>1.972768524088431</v>
       </c>
       <c r="C6" t="n">
-        <v>6.4794813929949</v>
+        <v>6.11450010079324</v>
       </c>
       <c r="D6" t="n">
-        <v>7.492665628533595</v>
+        <v>6.999376791346172</v>
       </c>
       <c r="E6" t="n">
-        <v>15.66199611850671</v>
+        <v>15.08664541622784</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.88420386188766</v>
+        <v>2.261472621819253</v>
       </c>
       <c r="C7" t="n">
-        <v>7.430199870922486</v>
+        <v>6.788753225406578</v>
       </c>
       <c r="D7" t="n">
-        <v>8.017630563950735</v>
+        <v>7.372815245984509</v>
       </c>
       <c r="E7" t="n">
-        <v>17.33203429676088</v>
+        <v>16.42304109321034</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.118685788078275</v>
+        <v>1.425888759022863</v>
       </c>
       <c r="C8" t="n">
-        <v>5.148552365935014</v>
+        <v>4.401799259219553</v>
       </c>
       <c r="D8" t="n">
-        <v>6.293667910199371</v>
+        <v>5.627094383308843</v>
       </c>
       <c r="E8" t="n">
-        <v>12.56090606421266</v>
+        <v>11.45478240155126</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.389972316740242</v>
+        <v>1.800117710136572</v>
       </c>
       <c r="C9" t="n">
-        <v>6.35605756668662</v>
+        <v>5.304560396375976</v>
       </c>
       <c r="D9" t="n">
-        <v>6.938590877381378</v>
+        <v>6.180398028436426</v>
       </c>
       <c r="E9" t="n">
-        <v>14.68462076080824</v>
+        <v>13.28507613494897</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.669299387774301</v>
+        <v>2.193502927799173</v>
       </c>
       <c r="C10" t="n">
-        <v>7.693838391461152</v>
+        <v>6.340944426990268</v>
       </c>
       <c r="D10" t="n">
-        <v>7.537214694307989</v>
+        <v>6.768663214084244</v>
       </c>
       <c r="E10" t="n">
-        <v>16.90035247354344</v>
+        <v>15.30311056887368</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.953499419535788</v>
+        <v>2.609061773537611</v>
       </c>
       <c r="C11" t="n">
-        <v>9.12067086143132</v>
+        <v>7.476028584197896</v>
       </c>
       <c r="D11" t="n">
-        <v>8.118079786565318</v>
+        <v>7.287066083660988</v>
       </c>
       <c r="E11" t="n">
-        <v>19.19225006753242</v>
+        <v>17.37215644139649</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.247388132394568</v>
+        <v>3.035952121832067</v>
       </c>
       <c r="C12" t="n">
-        <v>10.5901293797158</v>
+        <v>8.745658456112228</v>
       </c>
       <c r="D12" t="n">
-        <v>8.785152983664643</v>
+        <v>7.880664846838471</v>
       </c>
       <c r="E12" t="n">
-        <v>21.62267049577501</v>
+        <v>19.66227542478277</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.529917868447129</v>
+        <v>3.462945809135756</v>
       </c>
       <c r="C13" t="n">
-        <v>12.04449113793115</v>
+        <v>10.08619798971362</v>
       </c>
       <c r="D13" t="n">
-        <v>9.44937218887689</v>
+        <v>8.50503056930183</v>
       </c>
       <c r="E13" t="n">
-        <v>24.02378119525517</v>
+        <v>22.05417436815121</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.459760661444582</v>
+        <v>2.018944518829481</v>
       </c>
       <c r="C14" t="n">
-        <v>8.371166324571703</v>
+        <v>7.184861668668026</v>
       </c>
       <c r="D14" t="n">
-        <v>7.115638638041585</v>
+        <v>6.495095549141261</v>
       </c>
       <c r="E14" t="n">
-        <v>16.94656562405787</v>
+        <v>15.69890173663877</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.495133031228595</v>
+        <v>2.089296559315807</v>
       </c>
       <c r="C15" t="n">
-        <v>8.916821698592079</v>
+        <v>7.752262754337471</v>
       </c>
       <c r="D15" t="n">
-        <v>7.234911166630529</v>
+        <v>6.578200492305752</v>
       </c>
       <c r="E15" t="n">
-        <v>17.6468658964512</v>
+        <v>16.41975980595903</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.73608337028189</v>
+        <v>2.461388756702391</v>
       </c>
       <c r="C16" t="n">
-        <v>10.40552428235786</v>
+        <v>9.19199576261542</v>
       </c>
       <c r="D16" t="n">
-        <v>7.825020076699203</v>
+        <v>7.116482941067238</v>
       </c>
       <c r="E16" t="n">
-        <v>19.96662772933895</v>
+        <v>18.76986746038505</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.398234532819435</v>
+        <v>1.990709454855343</v>
       </c>
       <c r="C17" t="n">
-        <v>9.479854006977627</v>
+        <v>8.56073198878472</v>
       </c>
       <c r="D17" t="n">
-        <v>7.341587872173988</v>
+        <v>6.668599820912799</v>
       </c>
       <c r="E17" t="n">
-        <v>18.21967641197105</v>
+        <v>17.22004126455286</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.594132469724843</v>
+        <v>2.302699057787936</v>
       </c>
       <c r="C18" t="n">
-        <v>10.9611345780993</v>
+        <v>10.00803427186241</v>
       </c>
       <c r="D18" t="n">
-        <v>7.871348750862609</v>
+        <v>7.162772345322474</v>
       </c>
       <c r="E18" t="n">
-        <v>20.42661579868675</v>
+        <v>19.47350567497282</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.599698979207923</v>
+        <v>2.343598667146859</v>
       </c>
       <c r="C19" t="n">
-        <v>11.64932990129927</v>
+        <v>10.72652632921544</v>
       </c>
       <c r="D19" t="n">
-        <v>8.054857031740422</v>
+        <v>7.299834142312371</v>
       </c>
       <c r="E19" t="n">
-        <v>21.30388591224762</v>
+        <v>20.36995913867467</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.773919926803562</v>
+        <v>2.647636113675053</v>
       </c>
       <c r="C20" t="n">
-        <v>13.33125025073786</v>
+        <v>12.3507395485984</v>
       </c>
       <c r="D20" t="n">
-        <v>8.598912157002879</v>
+        <v>7.888951487199754</v>
       </c>
       <c r="E20" t="n">
-        <v>23.7040823345443</v>
+        <v>22.88732714947321</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.050705662993106</v>
+        <v>1.60120105319542</v>
       </c>
       <c r="C21" t="n">
-        <v>9.780651686081807</v>
+        <v>9.098975167638034</v>
       </c>
       <c r="D21" t="n">
-        <v>7.220901626890927</v>
+        <v>6.617637297585348</v>
       </c>
       <c r="E21" t="n">
-        <v>18.05225897596584</v>
+        <v>17.3178135184188</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_100_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_100_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.29088673911817</v>
+        <v>2.61381442714728</v>
       </c>
       <c r="C3" t="n">
-        <v>4.593938065684362</v>
+        <v>7.87498820420187</v>
       </c>
       <c r="D3" t="n">
-        <v>6.114349339676381</v>
+        <v>8.190493099616585</v>
       </c>
       <c r="E3" t="n">
-        <v>11.99917414447891</v>
+        <v>18.67929573096573</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.471097668225085</v>
+        <v>1.110729741663554</v>
       </c>
       <c r="C4" t="n">
-        <v>5.017043914170736</v>
+        <v>4.871056549719543</v>
       </c>
       <c r="D4" t="n">
-        <v>6.403424889629651</v>
+        <v>5.826425880384005</v>
       </c>
       <c r="E4" t="n">
-        <v>12.89156647202547</v>
+        <v>11.8082121717671</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.710078247576866</v>
+        <v>1.222811687752675</v>
       </c>
       <c r="C5" t="n">
-        <v>5.524204855809763</v>
+        <v>5.876615266392815</v>
       </c>
       <c r="D5" t="n">
-        <v>6.712130286668832</v>
+        <v>6.250965012491512</v>
       </c>
       <c r="E5" t="n">
-        <v>13.94641339005546</v>
+        <v>13.350391966637</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.972768524088431</v>
+        <v>1.352153030239519</v>
       </c>
       <c r="C6" t="n">
-        <v>6.11450010079324</v>
+        <v>7.090972079284811</v>
       </c>
       <c r="D6" t="n">
-        <v>6.999376791346172</v>
+        <v>6.680546343336881</v>
       </c>
       <c r="E6" t="n">
-        <v>15.08664541622784</v>
+        <v>15.12367145286121</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.261472621819253</v>
+        <v>1.484026297841254</v>
       </c>
       <c r="C7" t="n">
-        <v>6.788753225406578</v>
+        <v>8.435088751471888</v>
       </c>
       <c r="D7" t="n">
-        <v>7.372815245984509</v>
+        <v>7.138921926624661</v>
       </c>
       <c r="E7" t="n">
-        <v>16.42304109321034</v>
+        <v>17.0580369759378</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.425888759022863</v>
+        <v>1.620323084400253</v>
       </c>
       <c r="C8" t="n">
-        <v>4.401799259219553</v>
+        <v>9.887889356217498</v>
       </c>
       <c r="D8" t="n">
-        <v>5.627094383308843</v>
+        <v>7.590727837931489</v>
       </c>
       <c r="E8" t="n">
-        <v>11.45478240155126</v>
+        <v>19.09894027854924</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.800117710136572</v>
+        <v>1.73849849370906</v>
       </c>
       <c r="C9" t="n">
-        <v>5.304560396375976</v>
+        <v>11.51584576387418</v>
       </c>
       <c r="D9" t="n">
-        <v>6.180398028436426</v>
+        <v>8.065520782526368</v>
       </c>
       <c r="E9" t="n">
-        <v>13.28507613494897</v>
+        <v>21.31986504010961</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.193502927799173</v>
+        <v>1.073816003951076</v>
       </c>
       <c r="C10" t="n">
-        <v>6.340944426990268</v>
+        <v>8.230481878553135</v>
       </c>
       <c r="D10" t="n">
-        <v>6.768663214084244</v>
+        <v>6.348029743045087</v>
       </c>
       <c r="E10" t="n">
-        <v>15.30311056887368</v>
+        <v>15.6523276255493</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.609061773537611</v>
+        <v>1.003807575161236</v>
       </c>
       <c r="C11" t="n">
-        <v>7.476028584197896</v>
+        <v>8.964730986559324</v>
       </c>
       <c r="D11" t="n">
-        <v>7.287066083660988</v>
+        <v>6.242256245389537</v>
       </c>
       <c r="E11" t="n">
-        <v>17.37215644139649</v>
+        <v>16.2107948071101</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.035952121832067</v>
+        <v>1.071587436662436</v>
       </c>
       <c r="C12" t="n">
-        <v>8.745658456112228</v>
+        <v>10.71117179512102</v>
       </c>
       <c r="D12" t="n">
-        <v>7.880664846838471</v>
+        <v>6.701684718545916</v>
       </c>
       <c r="E12" t="n">
-        <v>19.66227542478277</v>
+        <v>18.48444395032937</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.462945809135756</v>
+        <v>0.8406803766235862</v>
       </c>
       <c r="C13" t="n">
-        <v>10.08619798971362</v>
+        <v>10.2033038902371</v>
       </c>
       <c r="D13" t="n">
-        <v>8.50503056930183</v>
+        <v>6.156048979479624</v>
       </c>
       <c r="E13" t="n">
-        <v>22.05417436815121</v>
+        <v>17.20003324634031</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.018944518829481</v>
+        <v>0.9021574178635215</v>
       </c>
       <c r="C14" t="n">
-        <v>7.184861668668026</v>
+        <v>11.96098571001242</v>
       </c>
       <c r="D14" t="n">
-        <v>6.495095549141261</v>
+        <v>6.543908044996412</v>
       </c>
       <c r="E14" t="n">
-        <v>15.69890173663877</v>
+        <v>19.40705117287235</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2.089296559315807</v>
+        <v>0.8665396111534474</v>
       </c>
       <c r="C15" t="n">
-        <v>7.752262754337471</v>
+        <v>12.89157454139093</v>
       </c>
       <c r="D15" t="n">
-        <v>6.578200492305752</v>
+        <v>6.599769489368056</v>
       </c>
       <c r="E15" t="n">
-        <v>16.41975980595903</v>
+        <v>20.35788364191243</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.461388756702391</v>
+        <v>0.9371763584740053</v>
       </c>
       <c r="C16" t="n">
-        <v>9.19199576261542</v>
+        <v>14.92267309679899</v>
       </c>
       <c r="D16" t="n">
-        <v>7.116482941067238</v>
+        <v>7.0215086681584</v>
       </c>
       <c r="E16" t="n">
-        <v>18.76986746038505</v>
+        <v>22.88135812343139</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.990709454855343</v>
+        <v>0.5552470490908686</v>
       </c>
       <c r="C17" t="n">
-        <v>8.56073198878472</v>
+        <v>11.04146117526077</v>
       </c>
       <c r="D17" t="n">
-        <v>6.668599820912799</v>
+        <v>5.851805365933538</v>
       </c>
       <c r="E17" t="n">
-        <v>17.22004126455286</v>
+        <v>17.44851359028518</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.302699057787936</v>
+        <v>0.4388510412753668</v>
       </c>
       <c r="C18" t="n">
-        <v>10.00803427186241</v>
+        <v>9.894848579039795</v>
       </c>
       <c r="D18" t="n">
-        <v>7.162772345322474</v>
+        <v>5.369600346038633</v>
       </c>
       <c r="E18" t="n">
-        <v>19.47350567497282</v>
+        <v>15.7032999663538</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.343598667146859</v>
+        <v>0.5104891712542565</v>
       </c>
       <c r="C19" t="n">
-        <v>10.72652632921544</v>
+        <v>12.11877220103897</v>
       </c>
       <c r="D19" t="n">
-        <v>7.299834142312371</v>
+        <v>5.881719218481938</v>
       </c>
       <c r="E19" t="n">
-        <v>20.36995913867467</v>
+        <v>18.51098059077516</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.647636113675053</v>
+        <v>0.5759226557423064</v>
       </c>
       <c r="C20" t="n">
-        <v>12.3507395485984</v>
+        <v>14.39329509971502</v>
       </c>
       <c r="D20" t="n">
-        <v>7.888951487199754</v>
+        <v>6.381654601915542</v>
       </c>
       <c r="E20" t="n">
-        <v>22.88732714947321</v>
+        <v>21.35087235737287</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.60120105319542</v>
+        <v>0.6311066941980196</v>
       </c>
       <c r="C21" t="n">
-        <v>9.098975167638034</v>
+        <v>16.6310220944359</v>
       </c>
       <c r="D21" t="n">
-        <v>6.617637297585348</v>
+        <v>6.792447293803534</v>
       </c>
       <c r="E21" t="n">
-        <v>17.3178135184188</v>
+        <v>24.05457608243746</v>
       </c>
     </row>
   </sheetData>
